--- a/activity_log.xlsx
+++ b/activity_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K340"/>
+  <dimension ref="A1:K447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14943,6 +14943,4586 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2025-10-10 17:16:59</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Button: admin_process_next</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>admin_process_next</t>
+        </is>
+      </c>
+      <c r="I341" t="b">
+        <v>1</v>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>e990c000</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2025-10-10 17:17:28</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Button: admin_update_status</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>admin_update_status</t>
+        </is>
+      </c>
+      <c r="I342" t="b">
+        <v>1</v>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>2878853f</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2025-10-10 17:18:09</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Button: admin_select_order:ORD202510051454541617</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>admin_select_order:ORD202510051454541617</t>
+        </is>
+      </c>
+      <c r="I343" t="b">
+        <v>1</v>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>b6a1ca15</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2025-10-10 17:18:17</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Button: admin_update_status</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>admin_update_status</t>
+        </is>
+      </c>
+      <c r="I344" t="b">
+        <v>1</v>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>237ea5d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2025-10-10 17:18:53</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Button: admin_order_dashboard</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>admin_order_dashboard</t>
+        </is>
+      </c>
+      <c r="I345" t="b">
+        <v>1</v>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>5ebdb1c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2025-10-10 17:19:16</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I346" t="b">
+        <v>1</v>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>06960eab</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2025-10-10 17:19:16</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>admin_welcome</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Admin welcome message sent</t>
+        </is>
+      </c>
+      <c r="I347" t="b">
+        <v>1</v>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>06960eab</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2025-10-10 17:19:24</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Button: admin_order_management</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>admin_order_management</t>
+        </is>
+      </c>
+      <c r="I348" t="b">
+        <v>1</v>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>b409d7c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2025-10-10 17:19:24</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>admin_order_management</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Order management menu sent</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>admin_order_management</t>
+        </is>
+      </c>
+      <c r="I349" t="b">
+        <v>1</v>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>b409d7c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2025-10-10 17:19:32</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Button: admin_recent_orders</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>admin_recent_orders</t>
+        </is>
+      </c>
+      <c r="I350" t="b">
+        <v>1</v>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>fecc8da1</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2025-10-10 17:20:48</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Button: admin_select_order:ORD202510070938371617</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>admin_select_order:ORD202510070938371617</t>
+        </is>
+      </c>
+      <c r="I351" t="b">
+        <v>1</v>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>c41cd75d</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2025-10-10 17:20:58</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Button: admin_update_status</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>admin_update_status</t>
+        </is>
+      </c>
+      <c r="I352" t="b">
+        <v>1</v>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>a40b1acb</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:43:28</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I353" t="b">
+        <v>0</v>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>1c607d15</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:43:29</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>welcome_message</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Welcome message sent</t>
+        </is>
+      </c>
+      <c r="I354" t="b">
+        <v>0</v>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>1c607d15</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:45:08</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I355" t="b">
+        <v>0</v>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>191003b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:45:09</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>welcome_message</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Welcome message sent</t>
+        </is>
+      </c>
+      <c r="I356" t="b">
+        <v>0</v>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>191003b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:45:40</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Button: browse_laptops</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I357" t="b">
+        <v>0</v>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>ab9e1cae</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:45:40</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Laptop catalog options sent</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I358" t="b">
+        <v>0</v>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>ab9e1cae</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:45:48</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Button: action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I359" t="b">
+        <v>0</v>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>2fa5c105</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:45:49</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>catalog_viewed</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Laptop catalog sent</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I360" t="b">
+        <v>0</v>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>2fa5c105</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>{"catalog_type": "laptops"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:46:07</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>order_placed</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Order placed: LAPTOP</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Order confirmation sent</t>
+        </is>
+      </c>
+      <c r="I361" t="b">
+        <v>0</v>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>f634d637</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>{"catalog_id": "796694820003872", "order_text": "", "products": [{"title": "Unnamed Product", "quantity": 1, "price": 385.0, "item_total": 385.0, "retailer_id": "i6s3jodpvd"}], "order_type": "LAPTOP", "laptop_count": 1, "repair_count": 0, "total_amount": 385.0, "order_id": "ORD202511020046071617"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:46:09</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>263718516319</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>admin_order_notification</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Order notification sent for LAPTOP order from 263776681617</t>
+        </is>
+      </c>
+      <c r="I362" t="b">
+        <v>1</v>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>f634d637</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>{"customer_phone": "263776681617", "customer_name": "Codeconel\ud83d\udc68\u200d\ud83d\udcbb", "order_type": "LAPTOP", "order_value": 385.0, "product_count": 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:46:12</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>admin_order_notification</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Order notification sent for LAPTOP order from 263776681617</t>
+        </is>
+      </c>
+      <c r="I363" t="b">
+        <v>1</v>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>f634d637</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>{"customer_phone": "263776681617", "customer_name": "Codeconel\ud83d\udc68\u200d\ud83d\udcbb", "order_type": "LAPTOP", "order_value": 385.0, "product_count": 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:46:13</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>order_confirmation_sent</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Order confirmation sent for LAPTOP</t>
+        </is>
+      </c>
+      <c r="I364" t="b">
+        <v>0</v>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>f634d637</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:46:27</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I365" t="b">
+        <v>1</v>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>2e976f26</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:46:27</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>admin_welcome</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Admin welcome message sent</t>
+        </is>
+      </c>
+      <c r="I366" t="b">
+        <v>1</v>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>2e976f26</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:46:39</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Button: admin_order_management</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>admin_order_management</t>
+        </is>
+      </c>
+      <c r="I367" t="b">
+        <v>1</v>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>1f632912</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:46:39</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>admin_order_management</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Order management menu sent</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>admin_order_management</t>
+        </is>
+      </c>
+      <c r="I368" t="b">
+        <v>1</v>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>1f632912</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:46:47</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Button: admin_recent_orders</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>admin_recent_orders</t>
+        </is>
+      </c>
+      <c r="I369" t="b">
+        <v>1</v>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>d9647c38</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:50:04</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Button: admin_view_all_orders</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>admin_view_all_orders</t>
+        </is>
+      </c>
+      <c r="I370" t="b">
+        <v>1</v>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>d2d0a23b</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:50:18</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Button: admin_select_order:ORD202510051454541617</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>admin_select_order:ORD202510051454541617</t>
+        </is>
+      </c>
+      <c r="I371" t="b">
+        <v>1</v>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>044a02fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:50:40</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Button: admin_update_status</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>admin_update_status</t>
+        </is>
+      </c>
+      <c r="I372" t="b">
+        <v>1</v>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>e979fd7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:51:41</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Button: admin_order_dashboard</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>admin_order_dashboard</t>
+        </is>
+      </c>
+      <c r="I373" t="b">
+        <v>1</v>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>5a51ed57</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:52:06</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I374" t="b">
+        <v>1</v>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>4898ce68</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:52:07</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>admin_welcome</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Admin welcome message sent</t>
+        </is>
+      </c>
+      <c r="I375" t="b">
+        <v>1</v>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>4898ce68</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:52:16</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Button: admin_catalog_management</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>admin_catalog_management</t>
+        </is>
+      </c>
+      <c r="I376" t="b">
+        <v>1</v>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>e9f5d7c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:52:16</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>admin_catalog_management</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Catalog management menu sent</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>admin_catalog_management</t>
+        </is>
+      </c>
+      <c r="I377" t="b">
+        <v>1</v>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>e9f5d7c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:52:37</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Button: admin_back_main</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>admin_back_main</t>
+        </is>
+      </c>
+      <c r="I378" t="b">
+        <v>1</v>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>8bef9230</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:52:58</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I379" t="b">
+        <v>0</v>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>6b51b8a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:52:58</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>welcome_message</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Welcome message sent</t>
+        </is>
+      </c>
+      <c r="I380" t="b">
+        <v>0</v>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>6b51b8a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:06:33</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Button: why_spectrax</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>why_spectrax</t>
+        </is>
+      </c>
+      <c r="I381" t="b">
+        <v>0</v>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>4c303b75</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:06:34</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>why_spectrax</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Why SpectraX message sent</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>why_spectrax</t>
+        </is>
+      </c>
+      <c r="I382" t="b">
+        <v>0</v>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>4c303b75</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:14:28</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Button: lifetime_support</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>lifetime_support</t>
+        </is>
+      </c>
+      <c r="I383" t="b">
+        <v>0</v>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>888b424f</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:14:29</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>lifetime_support</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Lifetime support info sent</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>lifetime_support</t>
+        </is>
+      </c>
+      <c r="I384" t="b">
+        <v>0</v>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>888b424f</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:25:33</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Button: browse_laptops</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I385" t="b">
+        <v>0</v>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>d4d7be14</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:25:34</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Laptop catalog options sent</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I386" t="b">
+        <v>0</v>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>d4d7be14</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:25:41</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Button: action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I387" t="b">
+        <v>0</v>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>675584aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:25:41</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>catalog_viewed</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Laptop catalog sent</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I388" t="b">
+        <v>0</v>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>675584aa</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>{"catalog_type": "laptops"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:27:51</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I389" t="b">
+        <v>0</v>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>0d1a6bbd</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:27:52</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>welcome_message</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Welcome message sent</t>
+        </is>
+      </c>
+      <c r="I390" t="b">
+        <v>0</v>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>0d1a6bbd</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:27:59</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Button: browse_laptops</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I391" t="b">
+        <v>0</v>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>a36503c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:28:00</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Laptop catalog options sent</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I392" t="b">
+        <v>0</v>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>a36503c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:28:06</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Button: action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I393" t="b">
+        <v>0</v>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>3821d833</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:28:06</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>catalog_viewed</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Laptop catalog sent</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I394" t="b">
+        <v>0</v>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>3821d833</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>{"catalog_type": "laptops"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:28:58</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Button: action_repairs</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>action_repairs</t>
+        </is>
+      </c>
+      <c r="I395" t="b">
+        <v>0</v>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>b20d77db</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:28:59</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>catalog_viewed</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Repair catalog sent</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>action_repairs</t>
+        </is>
+      </c>
+      <c r="I396" t="b">
+        <v>0</v>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>b20d77db</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>{"catalog_type": "repairs"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:29:32</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I397" t="b">
+        <v>0</v>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>0840250d</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:29:33</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>welcome_message</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Welcome message sent</t>
+        </is>
+      </c>
+      <c r="I398" t="b">
+        <v>0</v>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>0840250d</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:29:40</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Button: browse_laptops</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I399" t="b">
+        <v>0</v>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>517cda5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:29:40</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Laptop catalog options sent</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I400" t="b">
+        <v>0</v>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>517cda5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:29:47</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Button: action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I401" t="b">
+        <v>0</v>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>6c70e45b</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:29:47</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>catalog_viewed</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Laptop catalog sent</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I402" t="b">
+        <v>0</v>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>6c70e45b</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>{"catalog_type": "laptops"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:31:06</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I403" t="b">
+        <v>0</v>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>460fb484</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:31:06</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>welcome_message</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Welcome message sent</t>
+        </is>
+      </c>
+      <c r="I404" t="b">
+        <v>0</v>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>460fb484</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:31:13</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Button: browse_laptops</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I405" t="b">
+        <v>0</v>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>627f8132</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:31:14</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Laptop catalog options sent</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I406" t="b">
+        <v>0</v>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>627f8132</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:31:20</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Button: action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I407" t="b">
+        <v>0</v>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>55684b31</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:31:21</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>catalog_viewed</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Laptop catalog sent</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I408" t="b">
+        <v>0</v>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>55684b31</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>{"catalog_type": "laptops"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:42:54</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I409" t="b">
+        <v>0</v>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>c89a8229</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:42:55</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>welcome_message</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Welcome message sent</t>
+        </is>
+      </c>
+      <c r="I410" t="b">
+        <v>0</v>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>c89a8229</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:43:02</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Button: browse_laptops</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I411" t="b">
+        <v>0</v>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>e9f514d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:43:02</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Laptop catalog options sent</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I412" t="b">
+        <v>0</v>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>e9f514d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:43:10</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Button: action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I413" t="b">
+        <v>0</v>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>260f80f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:43:11</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>catalog_viewed</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Laptop catalog sent</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I414" t="b">
+        <v>0</v>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>260f80f7</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>{"catalog_type": "laptops"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:44:08</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>order_placed</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Order placed: LAPTOP</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Order confirmation sent</t>
+        </is>
+      </c>
+      <c r="I415" t="b">
+        <v>0</v>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>759be82a</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>{"catalog_id": "796694820003872", "order_text": "", "products": [{"title": "Unnamed Product", "quantity": 1, "price": 390.0, "item_total": 390.0, "retailer_id": "i6s3jodpvd"}], "order_type": "LAPTOP", "laptop_count": 1, "repair_count": 0, "total_amount": 390.0, "order_id": "ORD202511020144071617"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:44:10</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>263718516319</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>admin_order_notification</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Order notification sent for LAPTOP order from 263776681617</t>
+        </is>
+      </c>
+      <c r="I416" t="b">
+        <v>1</v>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>759be82a</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>{"customer_phone": "263776681617", "customer_name": "Codeconel\ud83d\udc68\u200d\ud83d\udcbb", "order_type": "LAPTOP", "order_value": 390.0, "product_count": 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:44:12</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>admin_order_notification</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Order notification sent for LAPTOP order from 263776681617</t>
+        </is>
+      </c>
+      <c r="I417" t="b">
+        <v>1</v>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>759be82a</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>{"customer_phone": "263776681617", "customer_name": "Codeconel\ud83d\udc68\u200d\ud83d\udcbb", "order_type": "LAPTOP", "order_value": 390.0, "product_count": 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:44:14</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>order_confirmation_sent</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Order confirmation sent for LAPTOP</t>
+        </is>
+      </c>
+      <c r="I418" t="b">
+        <v>0</v>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>759be82a</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:44:43</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I419" t="b">
+        <v>0</v>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>0790db54</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:44:43</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>welcome_message</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Welcome message sent</t>
+        </is>
+      </c>
+      <c r="I420" t="b">
+        <v>0</v>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>0790db54</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:44:51</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Button: browse_laptops</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I421" t="b">
+        <v>0</v>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>76638b2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:44:52</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Laptop catalog options sent</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I422" t="b">
+        <v>0</v>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>76638b2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:44:57</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Button: action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I423" t="b">
+        <v>0</v>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>1532def3</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:44:58</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>catalog_viewed</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Laptop catalog sent</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I424" t="b">
+        <v>0</v>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>1532def3</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>{"catalog_type": "laptops"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:38:37</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I425" t="b">
+        <v>0</v>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>0f4c261f</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:38:38</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>welcome_message</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Welcome message sent</t>
+        </is>
+      </c>
+      <c r="I426" t="b">
+        <v>0</v>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>0f4c261f</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:40:02</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I427" t="b">
+        <v>0</v>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>04015b45</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:40:03</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>welcome_message</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Welcome message sent</t>
+        </is>
+      </c>
+      <c r="I428" t="b">
+        <v>0</v>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>04015b45</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:40:28</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I429" t="b">
+        <v>0</v>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>3950a5c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:40:29</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>welcome_message</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Welcome message sent</t>
+        </is>
+      </c>
+      <c r="I430" t="b">
+        <v>0</v>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>3950a5c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:40:46</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Button: browse_laptops</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I431" t="b">
+        <v>0</v>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>f81cdf13</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:40:47</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Laptop catalog options sent</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I432" t="b">
+        <v>0</v>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>f81cdf13</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:40:53</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Button: action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I433" t="b">
+        <v>0</v>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>92f50931</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:40:54</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>catalog_viewed</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Laptop catalog sent</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I434" t="b">
+        <v>0</v>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>92f50931</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>{"catalog_type": "laptops"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:41:17</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Button: action_repairs</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>action_repairs</t>
+        </is>
+      </c>
+      <c r="I435" t="b">
+        <v>0</v>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>b675fdc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:41:18</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>catalog_viewed</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Repair catalog sent</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>action_repairs</t>
+        </is>
+      </c>
+      <c r="I436" t="b">
+        <v>0</v>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>b675fdc9</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>{"catalog_type": "repairs"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:41:43</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I437" t="b">
+        <v>0</v>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>119deb69</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:41:43</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>welcome_message</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Welcome message sent</t>
+        </is>
+      </c>
+      <c r="I438" t="b">
+        <v>0</v>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>119deb69</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:41:50</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Button: browse_laptops</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I439" t="b">
+        <v>0</v>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>e71a32df</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:41:50</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Laptop catalog options sent</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>browse_laptops</t>
+        </is>
+      </c>
+      <c r="I440" t="b">
+        <v>0</v>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>e71a32df</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:41:57</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Button: action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I441" t="b">
+        <v>0</v>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>108cb210</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:41:57</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>catalog_viewed</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Laptop catalog sent</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>action_buy_laptop</t>
+        </is>
+      </c>
+      <c r="I442" t="b">
+        <v>0</v>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>108cb210</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>{"catalog_type": "laptops"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:42:24</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>message_received</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Hi</t>
+        </is>
+      </c>
+      <c r="I443" t="b">
+        <v>1</v>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>ed2aba49</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:42:24</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>admin_welcome</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Admin welcome message sent</t>
+        </is>
+      </c>
+      <c r="I444" t="b">
+        <v>1</v>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>ed2aba49</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:42:32</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Button: admin_catalog_management</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>admin_catalog_management</t>
+        </is>
+      </c>
+      <c r="I445" t="b">
+        <v>1</v>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>01016d43</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:42:32</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>admin_catalog_management</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Catalog management menu sent</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>admin_catalog_management</t>
+        </is>
+      </c>
+      <c r="I446" t="b">
+        <v>1</v>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>01016d43</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2025-11-05 15:42:42</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>263711475883</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>SpectraX Eyewear</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>interactive_button</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Button: admin_view_stats</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>admin_view_stats</t>
+        </is>
+      </c>
+      <c r="I447" t="b">
+        <v>1</v>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>54a8f016</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
